--- a/Тест2/270.xlsx
+++ b/Тест2/270.xlsx
@@ -189,19 +189,19 @@
     <t xml:space="preserve">Eijkman sinovida termostat nega muntazam tekshiriladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Termostat tez sinib qoladi</t>
+    <t xml:space="preserve">Termostat tez sinib qolishi mumkin</t>
   </si>
   <si>
     <t xml:space="preserve">Ozgina og'ish ham natijani o'zgartiradi</t>
   </si>
   <si>
-    <t xml:space="preserve">Elektr sarfi ko'p bo'ladi</t>
+    <t xml:space="preserve">Elektr sarfi ko'p bo'lib ketadi</t>
   </si>
   <si>
     <t xml:space="preserve">Jurnal yozuvi talab qilinadi</t>
   </si>
   <si>
-    <t xml:space="preserve">Termostat rangi o'zgarib turadi</t>
+    <t xml:space="preserve">Termostat rangi tez o'zgarib turadi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Ozgina og'ish ham natijani o'zgartiradi. Harorat aniq nazorat qilinadi, chunki ozgina og'ish ham natijani o'zgartirishi mumkin. Manba: Mavzu materiali (270.docx).</t>
